--- a/artfynd/Björnberget NV artfynd.xlsx
+++ b/artfynd/Björnberget NV artfynd.xlsx
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16945070</v>
+        <v>120122500</v>
       </c>
       <c r="B2" t="n">
-        <v>91245</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Grundtjärn, Ång</t>
+          <t>Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>685051</v>
+        <v>684352</v>
       </c>
       <c r="R2" t="n">
-        <v>7093125</v>
+        <v>7093728</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -756,41 +756,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120122600</v>
+        <v>120122517</v>
       </c>
       <c r="B3" t="n">
-        <v>91245</v>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>684484</v>
+        <v>684307</v>
       </c>
       <c r="R3" t="n">
-        <v>7093785</v>
+        <v>7094164</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120122519</v>
+        <v>120122502</v>
       </c>
       <c r="B4" t="n">
-        <v>80111</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6461</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>684310</v>
+        <v>684280</v>
       </c>
       <c r="R4" t="n">
-        <v>7094174</v>
+        <v>7094021</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>16944729</v>
+        <v>120122510</v>
       </c>
       <c r="B5" t="n">
-        <v>80083</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,37 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Grundtjärn, Ång</t>
+          <t>Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>684498</v>
+        <v>684030</v>
       </c>
       <c r="R5" t="n">
-        <v>7093312</v>
+        <v>7093983</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1046,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2014-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2014-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1062,79 +1047,64 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>16944981</v>
+        <v>126380531</v>
       </c>
       <c r="B6" t="n">
-        <v>80112</v>
+        <v>79864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>1352</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Grundtjärn, Ång</t>
+          <t>Övre Nyland, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>684322</v>
+        <v>684348</v>
       </c>
       <c r="R6" t="n">
-        <v>7094066</v>
+        <v>7093975</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1158,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2014-08-29</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2014-08-29</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1177,38 +1147,38 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Carl Jansson, Rolf Nylinder</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120122500</v>
+        <v>120122509</v>
       </c>
       <c r="B7" t="n">
-        <v>78980</v>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,21 +1186,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>684352</v>
+        <v>684019</v>
       </c>
       <c r="R7" t="n">
-        <v>7093728</v>
+        <v>7093921</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,32 +1272,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120122515</v>
+        <v>120122512</v>
       </c>
       <c r="B8" t="n">
-        <v>91263</v>
+        <v>91872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>684273</v>
+        <v>684148</v>
       </c>
       <c r="R8" t="n">
-        <v>7094150</v>
+        <v>7094055</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,14 +1369,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120122603</v>
+        <v>120122516</v>
       </c>
       <c r="B9" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1434,10 +1404,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>684513</v>
+        <v>684307</v>
       </c>
       <c r="R9" t="n">
-        <v>7093798</v>
+        <v>7094164</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1464,12 +1434,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1496,10 +1466,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>16944725</v>
+        <v>16944730</v>
       </c>
       <c r="B10" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1531,10 +1501,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>684808</v>
+        <v>684322</v>
       </c>
       <c r="R10" t="n">
-        <v>7093212</v>
+        <v>7094066</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1580,17 +1550,17 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1608,10 +1578,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>16944723</v>
+        <v>120122514</v>
       </c>
       <c r="B11" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,17 +1609,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Grundtjärn, Ång</t>
+          <t>Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>685007</v>
+        <v>684273</v>
       </c>
       <c r="R11" t="n">
-        <v>7093193</v>
+        <v>7094092</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1673,12 +1643,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2014-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2014-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1689,76 +1659,61 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120122601</v>
+        <v>126380530</v>
       </c>
       <c r="B12" t="n">
-        <v>80112</v>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bjurholm, Ång</t>
+          <t>Övre Nyland, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>684484</v>
+        <v>684349</v>
       </c>
       <c r="R12" t="n">
-        <v>7093785</v>
+        <v>7093972</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1785,12 +1740,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1801,61 +1756,76 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Carl Jansson, Rolf Nylinder</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126380530</v>
+        <v>120122505</v>
       </c>
       <c r="B13" t="n">
-        <v>80083</v>
+        <v>80460</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Övre Nyland, Ång</t>
+          <t>Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>684349</v>
+        <v>684262</v>
       </c>
       <c r="R13" t="n">
-        <v>7093972</v>
+        <v>7094016</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1882,12 +1852,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1898,41 +1868,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Carl Jansson, Rolf Nylinder</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120122513</v>
+        <v>120122519</v>
       </c>
       <c r="B14" t="n">
-        <v>80112</v>
+        <v>80460</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1940,21 +1895,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1964,10 +1919,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>684244</v>
+        <v>684310</v>
       </c>
       <c r="R14" t="n">
-        <v>7094112</v>
+        <v>7094174</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2026,10 +1981,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120122498</v>
+        <v>16944981</v>
       </c>
       <c r="B15" t="n">
-        <v>92535</v>
+        <v>80461</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2037,37 +1992,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bjurholm, Ång</t>
+          <t>Grundtjärn, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>684478</v>
+        <v>684322</v>
       </c>
       <c r="R15" t="n">
-        <v>7093927</v>
+        <v>7094066</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2091,12 +2046,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2014-08-29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2014-08-29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2107,61 +2062,76 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>104556978</v>
+        <v>120122513</v>
       </c>
       <c r="B16" t="n">
-        <v>91265</v>
+        <v>80461</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Grundtjärnen, Ång</t>
+          <t>Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>684641</v>
+        <v>684244</v>
       </c>
       <c r="R16" t="n">
-        <v>7093694</v>
+        <v>7094112</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2188,12 +2158,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-10-18</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-10-18</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2208,22 +2178,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120122518</v>
+        <v>120122508</v>
       </c>
       <c r="B17" t="n">
-        <v>78739</v>
+        <v>58057</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2231,21 +2201,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>103031</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2225,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>684331</v>
+        <v>684033</v>
       </c>
       <c r="R17" t="n">
-        <v>7094168</v>
+        <v>7093930</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,32 +2287,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120122511</v>
+        <v>120122507</v>
       </c>
       <c r="B18" t="n">
-        <v>80043</v>
+        <v>79085</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229497</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>684098</v>
+        <v>684044</v>
       </c>
       <c r="R18" t="n">
-        <v>7094023</v>
+        <v>7093921</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2414,48 +2384,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>16944984</v>
+        <v>120122518</v>
       </c>
       <c r="B19" t="n">
-        <v>80112</v>
+        <v>79085</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Grundtjärn, Ång</t>
+          <t>Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>684500</v>
+        <v>684331</v>
       </c>
       <c r="R19" t="n">
-        <v>7093343</v>
+        <v>7094168</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2479,12 +2449,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2014-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2014-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2495,79 +2465,64 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>16944378</v>
+        <v>120122511</v>
       </c>
       <c r="B20" t="n">
-        <v>92529</v>
+        <v>80392</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4362</v>
+        <v>229497</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Grundtjärn, Ång</t>
+          <t>Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>685054</v>
+        <v>684098</v>
       </c>
       <c r="R20" t="n">
-        <v>7093213</v>
+        <v>7094023</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2591,12 +2546,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2014-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2014-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2611,22 +2566,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120122497</v>
+        <v>16944432</v>
       </c>
       <c r="B21" t="n">
-        <v>92563</v>
+        <v>89292</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2634,37 +2589,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5449</v>
+        <v>510</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bjurholm, Ång</t>
+          <t>Grundtjärn, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>684590</v>
+        <v>684506</v>
       </c>
       <c r="R21" t="n">
-        <v>7094035</v>
+        <v>7093355</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2688,12 +2643,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2014-08-29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2014-08-29</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2704,26 +2659,41 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120122591</v>
+        <v>16945071</v>
       </c>
       <c r="B22" t="n">
-        <v>92551</v>
+        <v>91909</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2731,37 +2701,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2059</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bjurholm, Ång</t>
+          <t>Grundtjärn, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>684550</v>
+        <v>684497</v>
       </c>
       <c r="R22" t="n">
-        <v>7093732</v>
+        <v>7093722</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2785,12 +2755,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2014-08-29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2014-08-29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2801,26 +2771,41 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120122609</v>
+        <v>104556981</v>
       </c>
       <c r="B23" t="n">
-        <v>78739</v>
+        <v>91909</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2828,34 +2813,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bjurholm, Ång</t>
+          <t>Grundtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>684568</v>
+        <v>684618</v>
       </c>
       <c r="R23" t="n">
-        <v>7093941</v>
+        <v>7093676</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2882,12 +2867,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2022-10-18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2022-10-18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2902,44 +2887,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120122510</v>
+        <v>120122591</v>
       </c>
       <c r="B24" t="n">
-        <v>91245</v>
+        <v>93213</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>2059</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2949,10 +2934,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>684030</v>
+        <v>684550</v>
       </c>
       <c r="R24" t="n">
-        <v>7093983</v>
+        <v>7093732</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2979,12 +2964,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3011,32 +2996,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120122598</v>
+        <v>120122593</v>
       </c>
       <c r="B25" t="n">
-        <v>5176</v>
+        <v>93213</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100526</v>
+        <v>2059</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3046,10 +3031,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>684461</v>
+        <v>684583</v>
       </c>
       <c r="R25" t="n">
-        <v>7093769</v>
+        <v>7093396</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3108,10 +3093,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>16944432</v>
+        <v>120122594</v>
       </c>
       <c r="B26" t="n">
-        <v>88654</v>
+        <v>93197</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3119,37 +3104,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>510</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Grundtjärn, Ång</t>
+          <t>Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>684506</v>
+        <v>684498</v>
       </c>
       <c r="R26" t="n">
-        <v>7093355</v>
+        <v>7093423</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3173,12 +3158,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2014-08-29</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2014-08-29</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3189,41 +3174,26 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>104556982</v>
+        <v>104556978</v>
       </c>
       <c r="B27" t="n">
-        <v>78980</v>
+        <v>91930</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3231,21 +3201,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3255,10 +3225,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>684620</v>
+        <v>684641</v>
       </c>
       <c r="R27" t="n">
-        <v>7093690</v>
+        <v>7093694</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3317,32 +3287,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120122499</v>
+        <v>120122596</v>
       </c>
       <c r="B28" t="n">
-        <v>78739</v>
+        <v>91872</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3352,10 +3322,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>684496</v>
+        <v>684500</v>
       </c>
       <c r="R28" t="n">
-        <v>7093897</v>
+        <v>7093584</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3382,12 +3352,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3414,14 +3384,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120122516</v>
+        <v>104556982</v>
       </c>
       <c r="B29" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3445,14 +3415,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bjurholm, Ång</t>
+          <t>Grundtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>684307</v>
+        <v>684620</v>
       </c>
       <c r="R29" t="n">
-        <v>7094164</v>
+        <v>7093690</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3479,12 +3449,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2022-10-18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2022-10-18</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3499,60 +3469,60 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>16944983</v>
+        <v>104556979</v>
       </c>
       <c r="B30" t="n">
-        <v>80112</v>
+        <v>79413</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>6450</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Grundtjärn, Ång</t>
+          <t>Grundtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>684985</v>
+        <v>684646</v>
       </c>
       <c r="R30" t="n">
-        <v>7093071</v>
+        <v>7093617</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3576,12 +3546,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2014-08-29</t>
+          <t>2022-10-18</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2014-08-29</t>
+          <t>2022-10-18</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3592,41 +3562,26 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120122514</v>
+        <v>16944725</v>
       </c>
       <c r="B31" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3654,17 +3609,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bjurholm, Ång</t>
+          <t>Grundtjärn, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>684273</v>
+        <v>684808</v>
       </c>
       <c r="R31" t="n">
-        <v>7094092</v>
+        <v>7093212</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3688,12 +3643,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2014-08-29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2014-08-29</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3704,48 +3659,63 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>16944617</v>
+        <v>16944726</v>
       </c>
       <c r="B32" t="n">
-        <v>80119</v>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3755,10 +3725,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>684905</v>
+        <v>684588</v>
       </c>
       <c r="R32" t="n">
-        <v>7093306</v>
+        <v>7093158</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3804,17 +3774,17 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -3832,48 +3802,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>104556979</v>
+        <v>16944729</v>
       </c>
       <c r="B33" t="n">
-        <v>79066</v>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6450</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Grundtjärnen, Ång</t>
+          <t>Grundtjärn, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>684646</v>
+        <v>684498</v>
       </c>
       <c r="R33" t="n">
-        <v>7093617</v>
+        <v>7093312</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3897,12 +3867,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2022-10-18</t>
+          <t>2014-08-29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2022-10-18</t>
+          <t>2014-08-29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3913,64 +3883,79 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120122593</v>
+        <v>16944980</v>
       </c>
       <c r="B34" t="n">
-        <v>92551</v>
+        <v>80461</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2059</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bjurholm, Ång</t>
+          <t>Grundtjärn, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>684583</v>
+        <v>684498</v>
       </c>
       <c r="R34" t="n">
-        <v>7093396</v>
+        <v>7093312</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3994,12 +3979,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2014-08-29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2014-08-29</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4010,48 +3995,63 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>16944728</v>
+        <v>16944984</v>
       </c>
       <c r="B35" t="n">
-        <v>80083</v>
+        <v>80461</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4061,10 +4061,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>684588</v>
+        <v>684500</v>
       </c>
       <c r="R35" t="n">
-        <v>7093158</v>
+        <v>7093343</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4110,17 +4110,17 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4138,10 +4138,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120122596</v>
+        <v>104556980</v>
       </c>
       <c r="B36" t="n">
-        <v>91210</v>
+        <v>80467</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4149,34 +4149,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bjurholm, Ång</t>
+          <t>Grundtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>684500</v>
+        <v>684648</v>
       </c>
       <c r="R36" t="n">
-        <v>7093584</v>
+        <v>7093619</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2022-10-18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2022-10-18</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4223,60 +4223,60 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120122502</v>
+        <v>16944617</v>
       </c>
       <c r="B37" t="n">
-        <v>91245</v>
+        <v>80468</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bjurholm, Ång</t>
+          <t>Grundtjärn, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>684280</v>
+        <v>684905</v>
       </c>
       <c r="R37" t="n">
-        <v>7094021</v>
+        <v>7093306</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4300,12 +4300,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2014-08-29</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2014-08-29</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4316,26 +4316,41 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126380531</v>
+        <v>120122600</v>
       </c>
       <c r="B38" t="n">
-        <v>79516</v>
+        <v>91909</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4343,34 +4358,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1352</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Övre Nyland, Ång</t>
+          <t>Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>684348</v>
+        <v>684484</v>
       </c>
       <c r="R38" t="n">
-        <v>7093975</v>
+        <v>7093785</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4397,12 +4412,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4413,41 +4428,26 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Carl Jansson, Rolf Nylinder</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>16945071</v>
+        <v>120122606</v>
       </c>
       <c r="B39" t="n">
-        <v>91245</v>
+        <v>93189</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4455,37 +4455,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>4361</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Grundtjärn, Ång</t>
+          <t>Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>684497</v>
+        <v>684552</v>
       </c>
       <c r="R39" t="n">
-        <v>7093722</v>
+        <v>7093912</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2014-08-29</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2014-08-29</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4525,76 +4525,61 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>104556980</v>
+        <v>120122498</v>
       </c>
       <c r="B40" t="n">
-        <v>80118</v>
+        <v>93197</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6463</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Grundtjärnen, Ång</t>
+          <t>Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>684648</v>
+        <v>684478</v>
       </c>
       <c r="R40" t="n">
-        <v>7093619</v>
+        <v>7093927</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4621,12 +4606,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2022-10-18</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2022-10-18</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4641,22 +4626,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120122517</v>
+        <v>120122608</v>
       </c>
       <c r="B41" t="n">
-        <v>79012</v>
+        <v>93197</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4664,21 +4649,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4688,10 +4673,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>684307</v>
+        <v>684563</v>
       </c>
       <c r="R41" t="n">
-        <v>7094164</v>
+        <v>7093942</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4718,12 +4703,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4750,32 +4735,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120122512</v>
+        <v>120122496</v>
       </c>
       <c r="B42" t="n">
-        <v>91210</v>
+        <v>93209</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>4366</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4785,10 +4770,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>684148</v>
+        <v>684590</v>
       </c>
       <c r="R42" t="n">
-        <v>7094055</v>
+        <v>7094035</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4847,32 +4832,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120122608</v>
+        <v>120122603</v>
       </c>
       <c r="B43" t="n">
-        <v>92535</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4882,10 +4867,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>684563</v>
+        <v>684513</v>
       </c>
       <c r="R43" t="n">
-        <v>7093942</v>
+        <v>7093798</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4944,32 +4929,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120122501</v>
+        <v>120122604</v>
       </c>
       <c r="B44" t="n">
-        <v>91263</v>
+        <v>80460</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>6461</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4979,10 +4964,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>684267</v>
+        <v>684530</v>
       </c>
       <c r="R44" t="n">
-        <v>7093768</v>
+        <v>7093816</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5009,12 +4994,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5041,10 +5026,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>16944980</v>
+        <v>120122601</v>
       </c>
       <c r="B45" t="n">
-        <v>80112</v>
+        <v>80461</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5072,17 +5057,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Grundtjärn, Ång</t>
+          <t>Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>684498</v>
+        <v>684484</v>
       </c>
       <c r="R45" t="n">
-        <v>7093312</v>
+        <v>7093785</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5106,12 +5091,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2014-08-29</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2014-08-29</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5122,63 +5107,48 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120122606</v>
+        <v>120122598</v>
       </c>
       <c r="B46" t="n">
-        <v>92527</v>
+        <v>5179</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4361</v>
+        <v>100526</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5188,10 +5158,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>684552</v>
+        <v>684461</v>
       </c>
       <c r="R46" t="n">
-        <v>7093912</v>
+        <v>7093769</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5250,32 +5220,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120122505</v>
+        <v>120122499</v>
       </c>
       <c r="B47" t="n">
-        <v>80111</v>
+        <v>79085</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6461</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5285,10 +5255,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>684262</v>
+        <v>684496</v>
       </c>
       <c r="R47" t="n">
-        <v>7094016</v>
+        <v>7093897</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5347,10 +5317,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>16944730</v>
+        <v>120122609</v>
       </c>
       <c r="B48" t="n">
-        <v>80083</v>
+        <v>79085</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5358,37 +5328,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Grundtjärn, Ång</t>
+          <t>Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>684322</v>
+        <v>684568</v>
       </c>
       <c r="R48" t="n">
-        <v>7094066</v>
+        <v>7093941</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5412,12 +5382,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2014-08-29</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2014-08-29</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5428,79 +5398,64 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120122496</v>
+        <v>16945070</v>
       </c>
       <c r="B49" t="n">
-        <v>92547</v>
+        <v>91909</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4366</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Bjurholm, Ång</t>
+          <t>Grundtjärn, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>684590</v>
+        <v>685051</v>
       </c>
       <c r="R49" t="n">
-        <v>7094035</v>
+        <v>7093125</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5524,12 +5479,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2014-08-29</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2014-08-29</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5540,64 +5495,79 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120122508</v>
+        <v>16944378</v>
       </c>
       <c r="B50" t="n">
-        <v>57761</v>
+        <v>93191</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103031</v>
+        <v>4362</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Bjurholm, Ång</t>
+          <t>Grundtjärn, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>684033</v>
+        <v>685054</v>
       </c>
       <c r="R50" t="n">
-        <v>7093930</v>
+        <v>7093213</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5621,12 +5591,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2014-08-29</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2014-08-29</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5641,60 +5611,60 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120122604</v>
+        <v>16944447</v>
       </c>
       <c r="B51" t="n">
-        <v>80111</v>
+        <v>93197</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6461</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Bjurholm, Ång</t>
+          <t>Grundtjärn, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>684530</v>
+        <v>684986</v>
       </c>
       <c r="R51" t="n">
-        <v>7093816</v>
+        <v>7093457</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5718,12 +5688,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2014-08-29</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2014-08-29</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5738,22 +5708,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120122507</v>
+        <v>16944448</v>
       </c>
       <c r="B52" t="n">
-        <v>78739</v>
+        <v>93197</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5761,37 +5731,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Bjurholm, Ång</t>
+          <t>Grundtjärn, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>684044</v>
+        <v>685306</v>
       </c>
       <c r="R52" t="n">
-        <v>7093921</v>
+        <v>7093548</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5815,12 +5785,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2014-08-29</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2014-08-29</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5835,26 +5805,26 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>16944447</v>
+        <v>16944449</v>
       </c>
       <c r="B53" t="n">
-        <v>92535</v>
+        <v>93197</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -5882,10 +5852,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>684986</v>
+        <v>685338</v>
       </c>
       <c r="R53" t="n">
-        <v>7093457</v>
+        <v>7093502</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5944,10 +5914,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>104556981</v>
+        <v>16944723</v>
       </c>
       <c r="B54" t="n">
-        <v>91245</v>
+        <v>80432</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5955,37 +5925,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Grundtjärnen, Ång</t>
+          <t>Grundtjärn, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>684618</v>
+        <v>685007</v>
       </c>
       <c r="R54" t="n">
-        <v>7093676</v>
+        <v>7093193</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6009,12 +5979,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2022-10-18</t>
+          <t>2014-08-29</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2022-10-18</t>
+          <t>2014-08-29</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6025,26 +5995,41 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120122594</v>
+        <v>16944982</v>
       </c>
       <c r="B55" t="n">
-        <v>92535</v>
+        <v>80461</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6052,37 +6037,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Bjurholm, Ång</t>
+          <t>Grundtjärn, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>684498</v>
+        <v>684945</v>
       </c>
       <c r="R55" t="n">
-        <v>7093423</v>
+        <v>7093048</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6106,12 +6091,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2014-08-29</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2014-08-29</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6122,26 +6107,41 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>16944982</v>
+        <v>16944983</v>
       </c>
       <c r="B56" t="n">
-        <v>80112</v>
+        <v>80461</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6173,10 +6173,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>684945</v>
+        <v>684985</v>
       </c>
       <c r="R56" t="n">
-        <v>7093048</v>
+        <v>7093071</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
